--- a/relationship_surveys/024_wedding_music_selection_survey--relationship_surveys.xlsx
+++ b/relationship_surveys/024_wedding_music_selection_survey--relationship_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -638,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>grand_entrance</t>
+          <t>mother_son</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Grand Entrance</t>
+          <t>Mother Son</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mother_son</t>
+          <t>mother_daughter</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mother Son</t>
+          <t>Mother Daughter</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mother_daughter</t>
+          <t>special_dance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mother Daughter</t>
+          <t>Special Dance</t>
         </is>
       </c>
     </row>
@@ -790,29 +790,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>special_dance</t>
+          <t>wedding_party</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Special Dance</t>
+          <t>Wedding Party</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>wedding_music_selection_survey_second_page_choices</t>
+          <t>wedding_music_selection_survey_third_page_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>wedding_party</t>
+          <t>beyoncé</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wedding Party</t>
+          <t>Beyoncé</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>beyoncé</t>
+          <t>bruno_mars</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Beyoncé</t>
+          <t>Bruno Mars</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bruno_mars</t>
+          <t>elvis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bruno Mars</t>
+          <t>Elvis</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>elvis</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Elvis</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>john</t>
+          <t>justin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Justin</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>justin</t>
+          <t>maroon_5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Maroon 5</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maroon_5</t>
+          <t>michael_jackson</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Maroon 5</t>
+          <t>Michael Jackson</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>michael_jackson</t>
+          <t>one_direction</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Michael Jackson</t>
+          <t>One Direction</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>one_direction</t>
+          <t>the_beatles</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>One Direction</t>
+          <t>The Beatles</t>
         </is>
       </c>
     </row>
@@ -960,29 +960,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>the_beatles</t>
+          <t>the_wedding_singer</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>The Beatles</t>
+          <t>The Wedding Singer</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>wedding_music_selection_survey_third_page_choices</t>
+          <t>wedding_music_selection_survey_fifth_page_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>the_wedding_singer</t>
+          <t>i'm_a_little_too_late</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The Wedding Singer</t>
+          <t>I'm a Little Too Late</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>i'm_a_little_too_late</t>
+          <t>i_choose_you</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>I'm a Little Too Late</t>
+          <t>I Choose You</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>i_choose_you</t>
+          <t>love_on_top</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>I Choose You</t>
+          <t>Love on Top</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>love_on_top</t>
+          <t>love_shack</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Love on Top</t>
+          <t>Love Shack</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>love_shack</t>
+          <t>something_like</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Love Shack</t>
+          <t>Something Like</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>something_like</t>
+          <t>that's_what_love</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Something Like</t>
+          <t>That's What Love</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>that's_what_love</t>
+          <t>the_wedding</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>That's What Love</t>
+          <t>The Wedding</t>
         </is>
       </c>
     </row>
@@ -1096,27 +1096,10 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>the_wedding</t>
+          <t>you're_in_love</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
-        <is>
-          <t>The Wedding</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>wedding_music_selection_survey_fifth_page_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>you're_in_love</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>You're in Love</t>
         </is>
